--- a/erp-server/erp-server-file/src/main/resources/excel/wms/subcontractReturn.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/subcontractReturn.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
-    <t>发料单号</t>
+    <t>退料单号</t>
+  </si>
+  <si>
+    <t>来源单号</t>
   </si>
   <si>
     <t>委外订单</t>
@@ -41,22 +44,19 @@
     <t>作废状态</t>
   </si>
   <si>
-    <t>发料类型</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>发料日期</t>
-  </si>
-  <si>
-    <t>收货数量</t>
-  </si>
-  <si>
-    <t>发料数量</t>
+    <t>父SKU</t>
+  </si>
+  <si>
+    <t>子SKU</t>
+  </si>
+  <si>
+    <t>子产品名称</t>
+  </si>
+  <si>
+    <t>退料日期</t>
+  </si>
+  <si>
+    <t>退料数量</t>
   </si>
   <si>
     <t>仓库</t>
@@ -68,21 +68,24 @@
     <t>备注</t>
   </si>
   <si>
-    <t>审核人(最新)</t>
-  </si>
-  <si>
     <t>创建人</t>
   </si>
   <si>
     <t>创建时间</t>
   </si>
   <si>
-    <t>审核完成时间</t>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>更新时间</t>
   </si>
   <si>
     <t>{.code}</t>
   </si>
   <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
     <t>{.subcontractOrderCode}</t>
   </si>
   <si>
@@ -92,7 +95,7 @@
     <t>{.invalidStatusName}</t>
   </si>
   <si>
-    <t>{.typeName}</t>
+    <t>{.parentSkuNo}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -101,13 +104,10 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.date}</t>
-  </si>
-  <si>
-    <t>{.receiveQty}</t>
-  </si>
-  <si>
-    <t>{.issueQty}</t>
+    <t>{.billDate}</t>
+  </si>
+  <si>
+    <t>{.returnQty}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>
@@ -119,16 +119,16 @@
     <t>{.remark}</t>
   </si>
   <si>
-    <t>{.approveUserName}</t>
-  </si>
-  <si>
     <t>{.createUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
   </si>
   <si>
-    <t>{.approveTime}</t>
+    <t>{.updateUserName}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
   </si>
 </sst>
 </file>
@@ -1062,23 +1062,21 @@
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="4" width="15.375" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="13.875" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="13.25" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
     <col min="11" max="11" width="28.75" customWidth="1"/>
     <col min="12" max="12" width="12.125" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="15.875" customWidth="1"/>
-    <col min="15" max="15" width="14.125" customWidth="1"/>
-    <col min="16" max="16" width="15.375" customWidth="1"/>
-    <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="15.375" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
